--- a/www/download/COUNTRY.DEU.rpO1.xlsx
+++ b/www/download/COUNTRY.DEU.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>Alemanha</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>0.731925086265228</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.534</t>
+          <t>0.769088761654336</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>0.885386722112306</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.488</t>
+          <t>0.898408000431061</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>0.938262378454218</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.432</t>
+          <t>1.08271977276317</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>1.11656986865627</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>1.05752964164908</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>0.884017010217504</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>0.803923182782427</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.585</t>
+          <t>0.803793923582443</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>0.796432000106346</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.669</t>
+          <t>0.72966072452248</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.679902074648032</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.716948695538313</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>37.601</t>
+          <t>2.13539828093552</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>37.498</t>
+          <t>2.02984609746032</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>37.463</t>
+          <t>1.94766018895637</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>37.911</t>
+          <t>1.9661588063342</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>38.424</t>
+          <t>2.11034167830958</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>39.144</t>
+          <t>2.02195086818658</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>39.316</t>
+          <t>1.95033679735139</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>39.096</t>
+          <t>1.95695296837311</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>38.726</t>
+          <t>2.05666964895683</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>38.88</t>
+          <t>2.02495477961977</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>38.835</t>
+          <t>2.01242234050907</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>39.075</t>
+          <t>1.86899049953022</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>39.724</t>
+          <t>1.78909929488055</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>40.45</t>
+          <t>1.72243471268231</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>40.85</t>
+          <t>1.7133754462836</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>33.852</t>
+          <t>3.80211877297636</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33.756</t>
+          <t>3.65751064229747</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.647</t>
+          <t>3.53697068914566</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>34.046</t>
+          <t>3.57322244461027</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>34.567</t>
+          <t>3.66747001037119</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>35.229</t>
+          <t>3.57418203760671</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>35.333</t>
+          <t>3.47099136409001</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.093</t>
+          <t>3.60808712562344</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>34.653</t>
+          <t>3.81492905777105</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>34.658</t>
+          <t>3.61329931986744</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>34.48</t>
+          <t>3.65970872578335</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>34.684</t>
+          <t>3.62192280494786</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>35.288</t>
+          <t>3.5669868706075</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>35.843</t>
+          <t>3.47328859938736</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>35.862</t>
+          <t>3.38454387920456</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>57679.197</t>
+          <t>6.01476844551256</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>56921.734</t>
+          <t>5.9171650798934</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56526.422</t>
+          <t>5.79546973034248</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>56997.003</t>
+          <t>5.7379763035876</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>57318.04</t>
+          <t>5.83678195602146</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>57658.023</t>
+          <t>5.76338889254493</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>57334.344</t>
+          <t>5.52164746140459</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>56510</t>
+          <t>5.5800404063178</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>55724</t>
+          <t>5.72880453221714</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>56044</t>
+          <t>6.04031920204021</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>55693</t>
+          <t>5.77234630369919</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>55862</t>
+          <t>5.69589230662807</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>56788</t>
+          <t>5.44936481183272</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>57721.711</t>
+          <t>5.48470779942033</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>56739.567</t>
+          <t>5.54224664212299</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>49333.493</t>
+          <t>110061297068338</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>48495.041</t>
+          <t>94542055568472.3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>47917.779</t>
+          <t>86290083549549.5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>48296.046</t>
+          <t>97330142559753.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>48623.541</t>
+          <t>102266186599350</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>48867.203</t>
+          <t>108555469993660</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>48588.388</t>
+          <t>114219295822503</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>47915</t>
+          <t>114796339378179</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>47126</t>
+          <t>130273893592652</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>47259</t>
+          <t>121176941640695</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>46689</t>
+          <t>109281646867671</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>46883</t>
+          <t>98637671004184.5</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>83487844065090.9</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>48410</t>
+          <t>64353263396668</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>46952.701</t>
+          <t>56337439118620.1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>29.24</t>
+          <t>24460025090457.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>29.44</t>
+          <t>21089896593413.9</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.65</t>
+          <t>18888096318943.2</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>30.92</t>
+          <t>21106496984278.1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.07</t>
+          <t>22084790129115.8</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>22500970850910.6</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.73</t>
+          <t>23741821119334.5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>24283764328625.1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>33.76</t>
+          <t>27658951805536.9</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>34.11</t>
+          <t>25236579619315.6</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>33.97</t>
+          <t>22311565823461.2</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>33.85</t>
+          <t>19596065519304.5</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>33.75</t>
+          <t>16438735371564.6</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>34.71</t>
+          <t>13745478458000.7</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>12804444051914.3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>59.45</t>
+          <t>1009929267.98184</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>59.53</t>
+          <t>913868989.819343</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>59.47</t>
+          <t>930288100.678485</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.47</t>
+          <t>1034173026.32117</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>58.84</t>
+          <t>1106216212.10733</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.38</t>
+          <t>1277253034.29196</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>57.85</t>
+          <t>1354342934.48506</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>56.95</t>
+          <t>1305313652.67091</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>55.05</t>
+          <t>1226122350.99768</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>56.01</t>
+          <t>992870801.844902</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>54.99</t>
+          <t>875404897.031259</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>55.31</t>
+          <t>724622278.615596</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>55.78</t>
+          <t>524719663.167355</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>358538712.233487</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>54.49</t>
+          <t>373700450.0506</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>11.31</t>
+          <t>3148484.28706616</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.03</t>
+          <t>3057556.1094305</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>2736093.29671419</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>2800270.0054195</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>11.09</t>
+          <t>2742743.03557084</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.35</t>
+          <t>2505302.09589735</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>11.42</t>
+          <t>2498707.70668959</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>2651705.52389423</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>11.19</t>
+          <t>3183219.35689374</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>9.89</t>
+          <t>3552278.23613045</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>11.04</t>
+          <t>3533188.11817926</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10.84</t>
+          <t>3630129.03446049</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>10.47</t>
+          <t>4053625.70871316</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>9.73</t>
+          <t>4456244.93386247</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>9.24</t>
+          <t>4299736.83045073</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>19.51</t>
+          <t>4947990.78960918</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>4773970.58300242</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>19.68</t>
+          <t>4265746.49761753</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>4366492.3181592</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>4276618.77351698</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>20.46</t>
+          <t>4002735.61084127</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20.83</t>
+          <t>3982415.76739053</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>21.34</t>
+          <t>4184757.32500611</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>22.79</t>
+          <t>4989834.1909519</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>23.38</t>
+          <t>5578568.70274526</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>22.95</t>
+          <t>5631552.66789105</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>22.34</t>
+          <t>5896206.47098969</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>6655382.51572019</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>22.71</t>
+          <t>6834821.26286791</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>6229475.65727599</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>63.61</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>63.71</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>63.11</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>62.81</t>
+          <t>3.34712982951139</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>62.32</t>
+          <t>3.26195613203209</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>61.95</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>60.88</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>60.81</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>59.98</t>
+          <t>3.22717304870097</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>61.89</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>61.97</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>61.08</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16.88</t>
+          <t>545091.443710321</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>16.71</t>
+          <t>534115.768423765</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.61</t>
+          <t>481628.808970487</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>16.06</t>
+          <t>487508.218568299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>16.63</t>
+          <t>475748.678829375</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>17.23</t>
+          <t>431506.788696572</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>420795.060472542</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>16.76</t>
+          <t>446076.710621606</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>16.33</t>
+          <t>524492.793947102</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>15.81</t>
+          <t>585167.597490354</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>17.08</t>
+          <t>584756.219184891</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>591668.458139547</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>16.03</t>
+          <t>669238.552231181</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>14.91</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.731925086265228</t>
+          <t>722557.754060534</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.769088761654336</t>
+          <t>624774.753922678</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.885386722112306</t>
+          <t>561360.487382032</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.898408000431061</t>
+          <t>619940.579929451</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.938262378454218</t>
+          <t>638898.085720941</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.08271977276317</t>
+          <t>638705.919864617</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11656986865627</t>
+          <t>671944.672666758</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05752964164908</t>
+          <t>691983.139903261</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.884017010217504</t>
+          <t>798169.041801199</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803923182782427</t>
+          <t>728160.298324068</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803793923582443</t>
+          <t>647087.175854444</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796432000106346</t>
+          <t>564988.626435949</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.72966072452248</t>
+          <t>465844.915312984</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679902074648032</t>
+          <t>383491.294199725</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716948695538313</t>
+          <t>357049.793913701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.363</t>
+          <t>-4153843242789.22</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>-3702831294415.57</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.143</t>
+          <t>-3295155840859.34</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-3569903652578.72</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>1.131</t>
+          <t>-3902029733418.78</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1.017</t>
+          <t>-4807318891330.86</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.005</t>
+          <t>-5295405685872.19</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.068</t>
+          <t>-4860101775811.77</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>-5558215802044.33</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1.415</t>
+          <t>-4813831501713.75</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>-3698143956240.05</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>1.444</t>
+          <t>-2581987247201.55</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>1.618</t>
+          <t>-1505406217770.17</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>-795838156017.864</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>1.735</t>
+          <t>-1807901947470.87</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.558</t>
+          <t>-3582859911374.14</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.502</t>
+          <t>-3180088355370.83</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.317</t>
+          <t>-2760036438546.71</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>-2915669912113.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>1.302</t>
+          <t>-2998999475976.44</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1.173</t>
+          <t>-3903472907227.35</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>-4265095529800.95</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>-4514094203892.32</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>-4876416294895.42</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1.639</t>
+          <t>-4250725365442.58</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>1.638</t>
+          <t>-3159998435134.08</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>1.677</t>
+          <t>-2292909881183.55</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>1.876</t>
+          <t>-1306124143534.7</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>2.097</t>
+          <t>-698278598765.175</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>-1822320026612.2</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8.512</t>
+          <t>-570983331415.083</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>8.276</t>
+          <t>-522742939044.742</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7.367</t>
+          <t>-535119402312.625</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7.401</t>
+          <t>-654233740465.115</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.184</t>
+          <t>-903030257442.339</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6.412</t>
+          <t>-903845984103.507</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.311</t>
+          <t>-1030310156071.24</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>6.739</t>
+          <t>-346007571919.454</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>8.105</t>
+          <t>-681799507148.907</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>9.144</t>
+          <t>-563106136271.17</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>9.183</t>
+          <t>-538145521105.968</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.438</t>
+          <t>-289077366017.997</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10.884</t>
+          <t>-199282074235.472</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-97559557252.6895</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14418079141.3346</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>4.29</t>
+          <t>3238848.97547686</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.148</t>
+          <t>2717447.08737156</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.708</t>
+          <t>2378640.66787985</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>3.767</t>
+          <t>2612719.87313718</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3.738</t>
+          <t>2777372.92645523</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3.399</t>
+          <t>2722136.6117322</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3.374</t>
+          <t>2786715.30470509</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>3.535</t>
+          <t>2910572.39346993</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4.292</t>
+          <t>3451322.76911484</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4.871</t>
+          <t>3057341.73024693</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>5.034</t>
+          <t>2735349.46993193</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>5.362</t>
+          <t>2340499.65127612</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>6.162</t>
+          <t>1886904.45881838</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>6.788</t>
+          <t>1514696.65138231</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>5.914</t>
+          <t>1380579.97388059</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2.284</t>
+          <t>3375925.41338842</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.208</t>
+          <t>2957529.60685262</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.959</t>
+          <t>2729116.72461695</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1.979</t>
+          <t>3062536.89481011</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1.929</t>
+          <t>3226725.16877784</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1.714</t>
+          <t>3300736.46605994</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.706</t>
+          <t>3488504.39897244</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.828</t>
+          <t>3591428.26436885</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2.205</t>
+          <t>4168452.26324236</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2.486</t>
+          <t>3868394.3607587</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>2.518</t>
+          <t>3469064.8960405</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2.635</t>
+          <t>3045914.78661208</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2.989</t>
+          <t>2522076.72640505</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>3.272</t>
+          <t>2077331.70417317</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2.986</t>
+          <t>1938266.07166524</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>213.54</t>
+          <t>577907.20701724</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>202.98</t>
+          <t>581114.496989226</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>194.77</t>
+          <t>569372.66299253</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>196.62</t>
+          <t>600858.480607013</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>211.03</t>
+          <t>600302.862251976</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>202.2</t>
+          <t>614536.849060768</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>195.03</t>
+          <t>636044.31902115</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>195.7</t>
+          <t>695201.351947121</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>205.67</t>
+          <t>839065.950346315</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>202.5</t>
+          <t>1007507.32754731</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>201.24</t>
+          <t>1095999.9529517</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>186.9</t>
+          <t>1258715.0600739</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>178.91</t>
+          <t>1510355.82197752</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>172.24</t>
+          <t>1671979.62800848</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>171.34</t>
+          <t>1265888.36750474</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>380.21</t>
+          <t>23153851489929.8</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>365.75</t>
+          <t>20777546135128.4</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>353.7</t>
+          <t>20478308861426.1</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>357.32</t>
+          <t>23887711200856.1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>366.75</t>
+          <t>25481227302533.2</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>357.42</t>
+          <t>29518320941793.8</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>347.1</t>
+          <t>32470093311663.4</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>360.81</t>
+          <t>33924763972178.6</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>381.49</t>
+          <t>38765198681635.9</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>361.33</t>
+          <t>37618225194577.6</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>365.97</t>
+          <t>35395527597878.4</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>362.19</t>
+          <t>33673880798090.6</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>356.7</t>
+          <t>29048535553407.4</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>347.33</t>
+          <t>23153129398890.9</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>338.45</t>
+          <t>18394257394440.4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>601.48</t>
+          <t>504027.545040582</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>591.72</t>
+          <t>498306.496186612</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>579.55</t>
+          <t>483107.582522955</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>573.8</t>
+          <t>510269.044784054</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>583.68</t>
+          <t>520999.817854744</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>576.34</t>
+          <t>548615.686679205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>552.16</t>
+          <t>543158.262380266</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>558</t>
+          <t>547031.874859046</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>572.88</t>
+          <t>670655.969606237</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>604.03</t>
+          <t>789020.360184291</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>577.23</t>
+          <t>865640.065505454</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>569.59</t>
+          <t>1003709.30337883</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>544.94</t>
+          <t>1170974.86363347</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>548.47</t>
+          <t>1323009.70758408</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>554.22</t>
+          <t>1004959.19095404</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>126938171.469</t>
+          <t>16303626360288.1</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>110901445.198</t>
+          <t>14379745472021.9</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>102240899.854</t>
+          <t>14307451468236.9</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>116103836.219</t>
+          <t>16920585455803.1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>123983687.885</t>
+          <t>18377162982675.2</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>129204028.227</t>
+          <t>21711362308983.5</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>137154038.95</t>
+          <t>22629538936301</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>140410479.424</t>
+          <t>22074732668898.1</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>161427482.346</t>
+          <t>25723420808687.5</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>150403172.746</t>
+          <t>24840651406003.1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>134721135.238</t>
+          <t>24232845414472.6</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>119019120.287</t>
+          <t>24047101714512.9</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>100186975.88</t>
+          <t>20639918366421.4</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>84028811.106</t>
+          <t>17110675373706.6</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>79177717.599</t>
+          <t>12726216615006.4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>109641515.518</t>
+          <t>73879.6619766577</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>91730143.881</t>
+          <t>82808.0008026142</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>80034122.552</t>
+          <t>86265.0804695758</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>88952660.801</t>
+          <t>90589.4358229591</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>96005449.949</t>
+          <t>79303.0443972323</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>95898150.695</t>
+          <t>65921.1623815622</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>98463011.861</t>
+          <t>92886.0566408838</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>102140717.004</t>
+          <t>148169.477088074</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>119598687.918</t>
+          <t>168409.980740078</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>105961349.687</t>
+          <t>218486.967363019</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>94314849.723</t>
+          <t>230359.88744625</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>81177889.905</t>
+          <t>255005.756695061</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>66585084.543</t>
+          <t>339380.958344055</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>54291272.075</t>
+          <t>348969.920424398</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>49510066.484</t>
+          <t>260929.176550695</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>110061297.068</t>
+          <t>6850225129641.73</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>94542055.568</t>
+          <t>6397800663106.46</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>86290083.55</t>
+          <t>6170857393189.18</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>97330142.56</t>
+          <t>6967125745052.97</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>102266186.599</t>
+          <t>7104064319858.03</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>108555469.994</t>
+          <t>7806958632810.28</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>114219295.823</t>
+          <t>9840554375362.4</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>114796339.378</t>
+          <t>11850031303280.5</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>130273893.593</t>
+          <t>13041777872948.4</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>121176941.641</t>
+          <t>12777573788574.5</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>109281646.868</t>
+          <t>11162682183405.8</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>98637671.004</t>
+          <t>9626779083577.69</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>83487844.065</t>
+          <t>8408617186985.92</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>64353263.397</t>
+          <t>6042454025184.34</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>56337439.119</t>
+          <t>5668040779434.05</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>4.948</t>
+          <t>1056023.36682</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4.774</t>
+          <t>1007321.96497</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>4.266</t>
+          <t>890469.64307</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4.366</t>
+          <t>897064.59083</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>4.277</t>
+          <t>862328.08299</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>4.003</t>
+          <t>768933.95974</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>3.982</t>
+          <t>758537.39575</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>4.185</t>
+          <t>805528.24857</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>961033.54614</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5.579</t>
+          <t>1094768.77747</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>5.632</t>
+          <t>1105569.44245</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>5.896</t>
+          <t>1168674.7893</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>6.655</t>
+          <t>1341856.5192</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>6.835</t>
+          <t>1447149.57748</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>6.229</t>
+          <t>1255690.97522</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>70033732.715</t>
+          <t>0.0212558615807381</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>60550779.393</t>
+          <t>0.020677897962817</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>55347339.394</t>
+          <t>0.021772737439555</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>62418678.192</t>
+          <t>0.0223277681371954</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>65586830.607</t>
+          <t>0.02104990949854</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>67944594.132</t>
+          <t>0.017205134338401</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>71665203.081</t>
+          <t>0.0200974746917341</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>72741634.367</t>
+          <t>0.0225876770416037</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>83107046.029</t>
+          <t>0.0248159113602402</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>77162124.453</t>
+          <t>0.0286209786496833</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>68562373.295</t>
+          <t>0.0321675624073745</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>60728448.904</t>
+          <t>0.0387971000529059</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>50850341.099</t>
+          <t>0.0407694859493459</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>41957776.65</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>38885481.739</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3.148</t>
+          <t>1363254.26397007</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3.058</t>
+          <t>1310121.86457592</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2.736</t>
+          <t>1142969.47780482</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>1150434.99498854</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2.743</t>
+          <t>1130675.20037073</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2.505</t>
+          <t>1017493.19579972</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2.499</t>
+          <t>1005060.25879547</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2.652</t>
+          <t>1068159.18640789</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>3.183</t>
+          <t>1281841.85530205</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3.552</t>
+          <t>1415296.91437412</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>1406878.01531334</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>3.63</t>
+          <t>1443676.29595017</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>4.054</t>
+          <t>1617724.45786562</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>4.456</t>
+          <t>1809250.3412473</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>1734712.46695596</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>24460025.09</t>
+          <t>1557974.55406545</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>21089896.593</t>
+          <t>1502412.29547561</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>18888096.319</t>
+          <t>1317411.14858811</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>21106496.984</t>
+          <t>1326358.61866775</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22084790.129</t>
+          <t>1302406.93863858</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>22500970.851</t>
+          <t>1172559.80554357</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23741821.119</t>
+          <t>1158039.93511591</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>24283764.329</t>
+          <t>1229729.51173504</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>27658951.806</t>
+          <t>1479553.94155057</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>25236579.619</t>
+          <t>1638875.00976356</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>22311565.823</t>
+          <t>1637759.62104069</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>19596065.519</t>
+          <t>1677285.14398029</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>16438735.372</t>
+          <t>1875703.64141804</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>13745478.458</t>
+          <t>2097001.03153539</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>12804444.052</t>
+          <t>2017691.93984275</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>8511749.96256924</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>8276300.33663781</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>7366901.39568792</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>7401377.1805815</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>7184357.139993</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>6412025.09902104</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>6310558.6501231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>6738992.81156657</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>8104710.03110398</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>9144246.35647392</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>9183339.8407178</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>9437534.09870476</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>10884321.7521092</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1009.929</t>
+          <t>1557974.55406545</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>913.869</t>
+          <t>1565823.16105272</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>930.288</t>
+          <t>1574515.97314039</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1034.173</t>
+          <t>1595825.50331131</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1106.216</t>
+          <t>1633583.99896788</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1277.253</t>
+          <t>1711168.19227524</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1354.343</t>
+          <t>1722289.03455401</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1305.314</t>
+          <t>1709599.1639397</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1226.122</t>
+          <t>1698931.65152834</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>992.871</t>
+          <t>1698284.98947203</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>875.405</t>
+          <t>1692748.03649668</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>724.622</t>
+          <t>1718338.36227257</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>524.72</t>
+          <t>1746733.59539946</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>358.539</t>
+          <t>1812032.68718169</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>373.7</t>
+          <t>1812740.50663989</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1363254.26397007</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1366629.34788592</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1367887.27938545</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1385840.64218068</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1418319.0540482</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1487220.49170109</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1498136.42213078</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>1487260.39086597</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>1473349.9808319</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1466778.69985087</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>1452908.41558482</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>1479614.55459368</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>1510272.60285515</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>1567941.67538722</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1559966.69082129</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>726016.022724546</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>705252.26229439</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>642026.418801891</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>652764.452152251</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>626978.746431417</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>541826.541906429</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>547621.353234095</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>598294.903834961</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>725618.559679428</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>846884.877226439</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>880161.876619309</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>957817.412819707</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>1112986.75497196</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>1175234.90225461</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>968030.770867249</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>109641515517843</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>91730143881314.4</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>80034122552153.3</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>88952660800828.4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>96005449948777.9</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>95898150694713.6</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>98463011861145.1</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>102140717004040</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>119598687918136</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>105961349686898</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>94314849723252.8</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>81177889904861</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>66585084542783</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>54291272075496.1</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>49510066483948.1</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>126938171468818</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>110901445197760</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>102240899854325</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>116103836219146</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>123983687885120</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>129204028227450</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>137154038950001</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>140410479423764</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>161427482346324</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>150403172746298</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>134721135237733</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>119019120286867</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>100186975879714</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>84028811106481.5</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>79177717598898.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>70033732714598.3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>60550779393303.7</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>55347339394099.8</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>62418678191602.4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>65586830607089</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>67944594131981.2</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>71665203081333.1</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>72741634367414.4</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>83107046028504.4</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>77162124453044.8</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>68562373295269.8</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>60728448904495.2</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>50850341098789</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>41957776649829.7</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>38885481738527.5</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>37601000</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>37498000</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>37463000</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>37911000</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>38424000</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>39144000</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>39316000</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>39096000</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>38726000</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>38880000</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>38835000</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>39075000</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>39724000</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>40450357.994188</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>40849767.096668</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>33852000</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>33756000</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>33647000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>34046000</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>34567000</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>35229000</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>35333000</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>35093000</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>34653000</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>34658000</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>34480000</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>34684000</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>35288000</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>35843000</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>35861788.1040119</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>57679196738.1535</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>56921734359.5757</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>56526421658.4249</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>56997003030.2113</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>57318039756.847</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>57658022765.4988</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>57334343544.1498</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>5.651e+10</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>5.5724e+10</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>5.6044e+10</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>5.5693e+10</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>5.5862e+10</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>5.6788e+10</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>57721710897.5781</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>56739567063.1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>49333493412.3921</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>48495041184.2737</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>47917778993.4606</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>48296045892.6359</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>48623541304.493</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>48867203486.7267</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>48588388114.2661</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>4.7915e+10</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>4.7126e+10</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4.7259e+10</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>4.6689e+10</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>4.6883e+10</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>4.7776e+10</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>4.841e+10</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>46952701355.6198</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.292360206508077</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.294446300408508</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.296502004060942</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.309167344856546</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.300709474163641</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.302691879989424</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.307297726488227</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.318450369437362</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.337570238433673</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.341056812054553</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.339734656467144</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.338469540174099</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.337491902506053</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.347081543739561</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.36261815887713</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.59454138680484</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.595258406339624</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.594653617929654</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.584727948123357</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.588371699399295</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.583821059901513</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.578503908321464</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.569470000808505</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.550528974734686</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.560057982965693</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.549858319779674</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.55309471873137</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.557789083181953</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.555608619892097</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.54494562514477</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.113098406687083</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.110295293251868</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.108844378009404</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.106104707020097</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.110918826437064</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.113487060109063</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.114198365190309</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.112079629754133</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.111900786831642</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.0988852049797545</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.110407023753181</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.108435741094531</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.104719014311994</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.0973098363683425</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.0924362159780996</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.195115628492194</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.195838904275002</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.196825263313754</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.208303944300909</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.20555775804634</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.204559713203882</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.208305012463317</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.213422469992099</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.227905040231277</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.233830997800985</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.22946619900437</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.22343403545077</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.220789162547975</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.227133454897749</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.24001300599493</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.63606301929354</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.637096976669119</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.637065756539099</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.631067282541124</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.628112529655099</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.623163264316266</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.619472028944092</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.618968233794798</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.608778533378536</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.608101359468275</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.599776482128622</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.606592253844489</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.618927960349674</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.619677145111692</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.610837209615879</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.168821352214266</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.167064119055879</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.166108980147147</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.160628773157967</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.166329712298562</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.172277022479852</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.172222958592591</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.167609296213104</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.163316426390187</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.15806764273074</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.170757318867008</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.169973710704741</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.160282877102351</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.153189399990559</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.149149784389191</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>4289714.99955</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4148350.8472</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>3708413.41752</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>3767286.13336</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>3737973.56792</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>3399402.20853</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>3373850.6568</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>3534860.73441</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>4292179.88478</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>4871137.04873</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>5034337.63434</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>5362002.02775</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>6161850.08853</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>6788492.30254</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>5913505.46421</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2283990.57679</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2207664.55777</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1959437.56739</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1979123.07082</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1929385.68507</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1714386.34745</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1705661.28835</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>1828024.41557</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>2205172.50123</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2485759.88699</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2517921.49766</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2635102.5568</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2988690.39639</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>3272235.93379</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2985722.71071</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>6229963.21060905</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>6404784.34412815</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>6577082.45551666</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>6759822.08704437</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>6956322.46315011</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>7155973.14476165</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>7327014.06849413</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>7460931.2845158</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>7586839.43485666</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>7701435.24330397</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>7833162.16535079</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>8009309.99162415</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>8201285.55467841</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
